--- a/SLR/Full-Paper-Read/Paper-Review/PS17.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS17.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="61">
   <si>
     <t>ID</t>
   </si>
@@ -26,112 +26,120 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>This paper presents an industrial case study on the application of the Arrowhead framework. The framework is implemented in the Machine Tooling ecosystem and enables the integration of grinding machines with other sensors, components or machines. Different software engineering tools offered with Arrowhead are used to design new solutions in Cyber-Physical System and Internet of Things in Industry 4.0 and make them Arrowhead compliant, for fast deployment of platforms and applications (Dockers) or for testing purposes (Management tool).</t>
+    <t>This paper analyses several large project on digital innovation, and develops a conceptual framwork for developing and organizing digital innovation ecosystems. The framework is centered around 6 concepts, innovation strategty, innovation organization, innovatio network, innovation process, innovation object, innovation infrasttucture. Using lessons learned, 21 design principles are derived in these 6 areas. This framework supporst collaboration in multidisciplinary activities. The paper is focused on agri-food ecosystems. The framework is based on experiences and lessons learned extract from 6 progressive eu projects, where the approach and principles have been iteratively tried and expanded upon</t>
+  </si>
+  <si>
+    <t>This paper is very similar to our SPE paper, only they analyse 6 projects instaed of just 1. Their focus is slightly different, focusing on innovation instead of collaboration, but collaboration is part of innovation. Likewise, they focus on the project level eco-system, close to AIDOaRt, and describe how that should be constructed to foster innovation inside an EU-project. As such, this is a very similar paper to the one we are doing, and probably could be related work.</t>
+  </si>
+  <si>
+    <t>CPS Case Study / Example availability</t>
+  </si>
+  <si>
+    <t>&gt;5</t>
   </si>
   <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
-    <t>CPS Case Study / Example availability</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
-      </rPr>
-      <t>https://productive40.eu/</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color rgb="FF000000"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> not accessible</t>
-    </r>
-  </si>
-  <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
-      </rPr>
-      <t>https://www.arrowhead.eu/arrowheadtools</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color rgb="FF000000"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve"> not accessible</t>
-    </r>
-  </si>
-  <si>
     <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
   </si>
   <si>
     <t>Data</t>
   </si>
   <si>
-    <t>Intelligence and automation</t>
-  </si>
-  <si>
     <t>Continuous software and system engineering</t>
   </si>
   <si>
+    <t>Others</t>
+  </si>
+  <si>
     <t>n.a.</t>
   </si>
   <si>
-    <t>Servitization: the process of creating value in products by adding services</t>
+    <t>Innovation, buisness models, transferance of knowledge, organisation</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ1?</t>
   </si>
   <si>
-    <t>Interoperability, Software and Hardware Engineering, Determine relevant data, Difficulties for adding new equipment (scalability)</t>
-  </si>
-  <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
-    <t>improving machine tool performance and optimizing manufacturing resources, to develop smart services on top of CPS, integrate third party applications, make production more efficient and predictable</t>
+    <t>Focus on user needs, a conceptual framework is presented focusing on common technical infrastructure, identifying value streams with user engagement, engaging right people at right time. Buisness models to drive use cases. Similar to AIDOaRt, they define a reference architecture where each use case implements a version of the reference architecture</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
-    <t>Partially</t>
-  </si>
-  <si>
-    <t>A company provides engineering services along electronic product development life cycle focusing in the development of sensors and CPS and a university provides interoperability platforms.</t>
+    <t>The following aspects defined by authors related to RQ2:
+DP1.1: focus a project on a particular domain, but embed it into a 
+cross-domain environment. 
+DP1.2: set clear, ambitious objectives to stimulate digital 
+transformation both at project/programme level and at use case 
+level. 
+DP1.3: create a collaboration space around common, open 
+platforms and underlying (cross-domain) architectures and 
+infrastructure. 
+DP1.4: develop a well-balanced ecosystem of technology 
+developers and end users, large and small players. 
+DP1.5: development should be driven by end-user acceptance, 
+common values and viable, shared business models. 
+DP1.6: develop an open ecosystem that is attractive for existing 
+and new players 
+DP2.1: develop large-scale projects with multiple well-delineated 
+use cases with attention to integration, standardization and 
+harmonization and facilitate mutual learning and creating 
+synergies. 
+DP2.2: use case projects should be independent and autonomous 
+to a certain extent, but be guided and supported at project/ 
+programme level in which common architectures, reuse of 
+platform components and standardization play a key role. 
+DP2.3: issues, transcending use cases, should be addressed at 
+project/programme level and possibly solved by umbrella 
+organizations and/or public authorities. 
+DP2.4: guide, monitor and steer use cases based on output 
+instead of time sheets.
+DP3.1: create ecosystems that are driven by large, influential 
+keystone players as a constant factor complemented by large 
+numbers of small creative players. 
+DP3.2: use independent network organizations to solve difficult 
+issues by competition and create level playing fields. 
+DP3.3: focus on integrated, shared value networks. 
+DP4.1: develop an iterative, lean MAA in use cases in which user 
+acceptance leads development of digital solutions. 
+DP4.2: facilitate reuse of knowledge, standards, data, models by 
+open, common architectures and infrastructures. 
+DP5.1: use state-of-the-art digital technology, knowledge and 
+experience. 
+DP5.2: build solutions based on common, open platforms using 
+GEs where possible. 
+DP5.3: interactive, and integrated approach towards product, 
+process and business innovation. 
+DP6.1: pull-push mechanisms to develop common core platforms 
+in which end applications in use cases ultimately validate them. 
+DP6.2: stimulate the use of domain-independent GEs as much as 
+possible, but remain flexible when developing end-user 
+solutions. 
+DP6.3: set up and foster developer communities and 
+experimental laboratory environments.</t>
   </si>
   <si>
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Machine Tooling ecosystem: integration of grinding machines with other sensors, components or machines</t>
+    <t>Aggriculture, farming, buisness ecosystems, organisation, project management</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
+  </si>
+  <si>
+    <t>Very high quality paper</t>
   </si>
   <si>
     <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
@@ -243,7 +251,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -269,13 +277,6 @@
       <name val="Arial"/>
     </font>
     <font/>
-    <font>
-      <i/>
-      <u/>
-      <sz val="10.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -502,13 +503,11 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -516,11 +515,13 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -633,7 +634,7 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -646,29 +647,35 @@
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="17" fillId="5" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="18" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="17" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -677,87 +684,81 @@
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="17" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="22" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="23" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1055,7 +1056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="82.5" customHeight="1">
+    <row r="3" ht="130.5" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1073,8 +1074,8 @@
       <c r="B4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17">
-        <v>1.0</v>
+      <c r="C4" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1082,7 +1083,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1090,18 +1091,18 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
-      <c r="I5" s="19" t="s">
-        <v>10</v>
+      <c r="I5" s="21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1120,16 +1121,16 @@
       <c r="E6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="23" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1140,35 +1141,35 @@
       <c r="B7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
+      <c r="C7" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="18"/>
-      <c r="I7" s="22" t="s">
-        <v>18</v>
+      <c r="I7" s="26" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="23" t="s">
         <v>19</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="22" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1176,18 +1177,18 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="29" t="s">
         <v>21</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="27" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1195,28 +1196,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="22" t="s">
-        <v>26</v>
+      <c r="I10" s="23" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1224,30 +1225,30 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="30">
+        <v>24</v>
+      </c>
+      <c r="C11" s="32">
         <f>Quality!C29</f>
-        <v>7.592592593</v>
-      </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="31" t="s">
-        <v>5</v>
+        <v>9.444444444</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="29" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="32" t="s">
-        <v>28</v>
+      <c r="B14" s="33" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="32" t="s">
-        <v>29</v>
+      <c r="B15" s="33" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2284,14 +2285,10 @@
       <formula1>"n.a.,Y,N"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="I4"/>
-    <hyperlink r:id="rId2" ref="I5"/>
-  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2310,83 +2307,83 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="33"/>
-      <c r="B1" s="34" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="B2" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="35"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="38" t="s">
+      <c r="C2" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="42"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="43"/>
+      <c r="B3" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="C3" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="42"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="43"/>
+      <c r="B4" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="40">
+      <c r="C4" s="41">
         <v>1.0</v>
       </c>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="41"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="42"/>
-      <c r="B3" s="39" t="s">
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="43"/>
+      <c r="B5" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="40">
+      <c r="C5" s="41">
         <v>1.0</v>
       </c>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="41"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="42"/>
-      <c r="B4" s="39" t="s">
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="43"/>
+      <c r="B6" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="40">
+      <c r="C6" s="41">
         <v>1.0</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="42"/>
-      <c r="B5" s="39" t="s">
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="44"/>
+      <c r="B7" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C7" s="41">
         <v>1.0</v>
-      </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="42"/>
-      <c r="B6" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="43"/>
-      <c r="B7" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="44">
-        <v>0.5</v>
       </c>
       <c r="D7" s="45">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
@@ -2394,139 +2391,139 @@
       </c>
       <c r="E7" s="45">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>9.166666667</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="43"/>
+      <c r="B9" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="C9" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="43"/>
+      <c r="B10" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="48">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="42"/>
-      <c r="B9" s="47" t="s">
+      <c r="C10" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="43"/>
+      <c r="B11" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="48">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="42"/>
-      <c r="B10" s="47" t="s">
+      <c r="C11" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="43"/>
+      <c r="B12" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="48">
-        <v>0.5</v>
-      </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="42"/>
-      <c r="B11" s="47" t="s">
+      <c r="C12" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="43"/>
+      <c r="B13" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="42"/>
-      <c r="B12" s="47" t="s">
+      <c r="C13" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="43"/>
+      <c r="B14" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="48">
-        <v>0.5</v>
-      </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="42"/>
-      <c r="B13" s="47" t="s">
+      <c r="C14" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="43"/>
+      <c r="B15" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C15" s="48">
         <v>1.0</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="42"/>
-      <c r="B14" s="47" t="s">
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="43"/>
+      <c r="B16" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C16" s="48">
         <v>1.0</v>
       </c>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="42"/>
-      <c r="B15" s="47" t="s">
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="43"/>
+      <c r="B17" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="42"/>
-      <c r="B16" s="47" t="s">
+      <c r="C17" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="43"/>
+      <c r="B18" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="48">
-        <v>0.0</v>
-      </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="42"/>
-      <c r="B17" s="47" t="s">
+      <c r="C18" s="48">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="44"/>
+      <c r="B19" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C19" s="48">
         <v>1.0</v>
-      </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="42"/>
-      <c r="B18" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="43"/>
-      <c r="B19" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="48">
-        <v>0.5</v>
       </c>
       <c r="D19" s="45">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
@@ -2534,72 +2531,72 @@
       </c>
       <c r="E19" s="45">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>5.416666667</v>
+        <v>9.583333333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="52">
         <v>1.0</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
     </row>
     <row r="21">
-      <c r="A21" s="42"/>
+      <c r="A21" s="43"/>
       <c r="B21" s="51" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C21" s="53">
         <v>0.5</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
     </row>
     <row r="22">
-      <c r="A22" s="42"/>
+      <c r="A22" s="43"/>
       <c r="B22" s="51" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C22" s="52">
         <v>1.0</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
     </row>
     <row r="23">
-      <c r="A23" s="42"/>
+      <c r="A23" s="43"/>
       <c r="B23" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="41"/>
+        <v>54</v>
+      </c>
+      <c r="C23" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="42"/>
     </row>
     <row r="24">
-      <c r="A24" s="42"/>
+      <c r="A24" s="43"/>
       <c r="B24" s="51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C24" s="52">
         <v>1.0</v>
       </c>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="41"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="42"/>
     </row>
     <row r="25">
-      <c r="A25" s="43"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C25" s="52">
         <v>1.0</v>
@@ -2610,40 +2607,40 @@
       </c>
       <c r="E25" s="54">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>9.166666667</v>
-      </c>
-      <c r="F25" s="41"/>
+        <v>8.333333333</v>
+      </c>
+      <c r="F25" s="42"/>
     </row>
     <row r="26">
       <c r="A26" s="55" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C26" s="57">
         <v>1.0</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="41"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="42"/>
     </row>
     <row r="27">
-      <c r="A27" s="42"/>
+      <c r="A27" s="43"/>
       <c r="B27" s="56" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C27" s="57">
         <v>1.0</v>
       </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="41"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="42"/>
     </row>
     <row r="28">
-      <c r="A28" s="43"/>
+      <c r="A28" s="44"/>
       <c r="B28" s="56" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C28" s="57">
         <v>1.0</v>
@@ -2656,7 +2653,7 @@
         <f>(SUM(C26:C28)/D28)*10</f>
         <v>10</v>
       </c>
-      <c r="F28" s="41"/>
+      <c r="F28" s="42"/>
     </row>
     <row r="29">
       <c r="B29" s="58">
@@ -2665,7 +2662,7 @@
       </c>
       <c r="C29" s="58">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>7.592592593</v>
+        <v>9.444444444</v>
       </c>
     </row>
   </sheetData>
